--- a/claims_log.xlsx
+++ b/claims_log.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 07:21:58</t>
+          <t>2026-07-09 08:29:11</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,114 @@
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 07:56:31</t>
+          <t>2026-07-09 08:44:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>POL-2025-30099</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Rahul Verma</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>01-Jan-2025 to 31-Dec-2025</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>08-Jul-2026</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Marathahalli, Bengaluru</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Claimant sustained a leg INJURY after a fall; investigators noted the scene looked STAGED upon review.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Rahul Verma</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>rahul.verma@email.com, +91-9567891234</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>INJURY</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>medical_report.pdf</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>Investigation Flag</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>Routed to Investigation Flag because the incident description contains flagged keyword(s): staged.</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>regex_fallback</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 08:29:49</t>
         </is>
       </c>
     </row>

--- a/claims_log.xlsx
+++ b/claims_log.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1371,6 +1371,113 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>POL-2024-55011</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Vikram Singh</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>01-Jan-2024 to 31-Dec-2024</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20-Jun-2026</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Outer Ring Road, Bengaluru</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Vehicle found burned in an isolated area. Witness statements appear inconsistent and the scene looks staged.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Vikram Singh</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Unknown witness</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>vikram.singh@email.com, +91-9988776655</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>KA-01-AB-1234</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>380000</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Vehicle Damage</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>incident_photos.zip</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>380000</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>Investigation Flag</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>Routed to Investigation Flag because the incident description contains flagged keyword(s): inconsistent, staged.</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>regex_fallback</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 10:10:43</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
